--- a/artfynd/A 56632-2021 artfynd.xlsx
+++ b/artfynd/A 56632-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56632-2021 artfynd.xlsx
+++ b/artfynd/A 56632-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,6 +950,141 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121428235</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56245</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Låsberget49, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>493766</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6672797</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Hygge</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Adina Sennblad (AFRY)</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Adina Sennblad (AFRY), Molly Wikingson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Artkartering Fladdermöss Låsberget</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56632-2021 artfynd.xlsx
+++ b/artfynd/A 56632-2021 artfynd.xlsx
@@ -955,7 +955,7 @@
         <v>121428235</v>
       </c>
       <c r="B4" t="n">
-        <v>56245</v>
+        <v>56248</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 56632-2021 artfynd.xlsx
+++ b/artfynd/A 56632-2021 artfynd.xlsx
@@ -955,7 +955,7 @@
         <v>121428235</v>
       </c>
       <c r="B4" t="n">
-        <v>56248</v>
+        <v>56249</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 56632-2021 artfynd.xlsx
+++ b/artfynd/A 56632-2021 artfynd.xlsx
@@ -955,7 +955,7 @@
         <v>121428235</v>
       </c>
       <c r="B4" t="n">
-        <v>56249</v>
+        <v>56250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 56632-2021 artfynd.xlsx
+++ b/artfynd/A 56632-2021 artfynd.xlsx
@@ -955,7 +955,7 @@
         <v>121428235</v>
       </c>
       <c r="B4" t="n">
-        <v>56250</v>
+        <v>56251</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
